--- a/Result/profitability/5388.xlsx
+++ b/Result/profitability/5388.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>1.155</v>
+        <v>1.12375</v>
       </c>
       <c r="N2" t="n">
-        <v>16.1175</v>
+        <v>15.40625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0075</v>
+        <v>0.99</v>
       </c>
       <c r="N3" t="n">
-        <v>15.85625</v>
+        <v>15.135</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.825</v>
+        <v>0.895</v>
       </c>
       <c r="N4" t="n">
-        <v>15.35375</v>
+        <v>14.50875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7525000000000001</v>
+        <v>0.80875</v>
       </c>
       <c r="N5" t="n">
-        <v>15.13</v>
+        <v>14.595</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>15.135</v>
+        <v>14.89625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.52125</v>
+        <v>0.6062500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>15.4</v>
+        <v>15.19125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4662500000000001</v>
+        <v>0.5375</v>
       </c>
       <c r="N8" t="n">
-        <v>15.825</v>
+        <v>15.655</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20616</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18080</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2536</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>678</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-70</v>
+      </c>
+      <c r="J75" t="n">
+        <v>607</v>
+      </c>
+      <c r="K75" t="n">
+        <v>473</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.27375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5643564356435644</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.359999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09956076134699854</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3982300884955754</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.279999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.258142340168878</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
